--- a/output/pdf_financials_xlsx/DC.A.xlsx
+++ b/output/pdf_financials_xlsx/DC.A.xlsx
@@ -1992,28 +1992,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>41.824</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>183.825</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>245.803</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>211.901</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>75.61499999999999</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>75.27800000000001</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>52.787</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>26.536</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>93.85299999999999</v>
@@ -2084,28 +2084,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>41.824</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>183.825</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>245.803</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>211.901</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>75.61499999999999</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>75.27800000000001</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>52.787</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>26.536</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>93.85299999999999</v>
@@ -12641,7 +12641,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
@@ -37714,7 +37714,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -39427,7 +39427,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -41242,7 +41242,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -45092,7 +45092,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -46830,7 +46830,7 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -48072,7 +48072,7 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -49202,7 +49202,7 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
@@ -50569,7 +50569,7 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
@@ -51853,7 +51853,7 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
@@ -52738,7 +52738,7 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
@@ -55705,7 +55705,7 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E624" s="5" t="n">

--- a/output/pdf_financials_xlsx/DC.A.xlsx
+++ b/output/pdf_financials_xlsx/DC.A.xlsx
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>6.43</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-45.953</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>51.227</v>
+        <v>-51.227</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>60.637</v>
+        <v>-60.637</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-9.314</v>
@@ -1338,28 +1338,30 @@
         <v>15.916</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>5.466</v>
+        <v>-103.778</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>41.49</v>
+        <v>-348.628</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-577.217</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-150.674</v>
+        <v>-133.919</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-70.387</v>
+        <v>-1.129</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>-209.129</v>
+        <v>-205.817</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-20.739</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>-100.898</v>
+        <v>-19.408</v>
+      </c>
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K20" s="3" t="n">
         <v>28.993</v>
@@ -1405,13 +1407,13 @@
         <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0</v>
+        <v>-8.992000000000001</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>-13.006</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0</v>
+        <v>-0.248</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>0</v>
@@ -1473,10 +1475,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>22.346</v>
+        <v>28.776</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-149.731</v>
+        <v>-195.684</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-348.628</v>
@@ -1891,10 +1893,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>28.77472478295892</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-30.69037139937621</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-12.81139413037226</v>
@@ -1937,10 +1939,10 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>10.4311375009336</v>
+        <v>13.43266860855926</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>-74.61256341003997</v>
+        <v>-97.5114362311763</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>-111.9305996121592</v>
@@ -5099,10 +5101,10 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>22.346</v>
+        <v>28.776</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>-149.731</v>
+        <v>-195.684</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>-348.628</v>
@@ -39836,7 +39838,11 @@
           <t>NET LOSS FROM DISCONTINUED OPERATIONS</t>
         </is>
       </c>
-      <c r="D425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E425" t="inlineStr">
         <is>
           <t>-</t>
@@ -41489,7 +41495,11 @@
           <t>Income tax recovery (expense) 20</t>
         </is>
       </c>
-      <c r="D446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E446" t="inlineStr">
         <is>
           <t>-</t>
@@ -41730,7 +41740,11 @@
           <t>NET (LOSS) FROM DISCONTINUED OPERATIONS</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E449" t="inlineStr">
         <is>
           <t>-</t>
@@ -45657,7 +45671,11 @@
           <t>NET LOSS FROM DISCONTINUED OPERATIONS</t>
         </is>
       </c>
-      <c r="D498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E498" t="inlineStr">
         <is>
           <t>-</t>
@@ -47148,7 +47166,11 @@
           <t>NET LOSS FROM CONTINUING OPERATIONS</t>
         </is>
       </c>
-      <c r="D517" t="inlineStr"/>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E517" t="inlineStr">
         <is>
           <t>-</t>
@@ -49449,7 +49471,11 @@
           <t>NET LOSS FROM CONTINUING OPERATIONS</t>
         </is>
       </c>
-      <c r="D546" t="inlineStr"/>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E546" t="inlineStr">
         <is>
           <t>-</t>
@@ -50650,7 +50676,11 @@
           <t>Income tax recovery 28</t>
         </is>
       </c>
-      <c r="D561" t="inlineStr"/>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E561" t="inlineStr">
         <is>
           <t>-</t>
@@ -51934,7 +51964,11 @@
           <t>Income tax recovery 29</t>
         </is>
       </c>
-      <c r="D577" t="inlineStr"/>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E577" t="inlineStr">
         <is>
           <t>-</t>
@@ -52985,7 +53019,11 @@
           <t>Income tax recovery 29</t>
         </is>
       </c>
-      <c r="D590" t="inlineStr"/>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E590" t="inlineStr">
         <is>
           <t>-</t>
@@ -53064,7 +53102,11 @@
           <t>NET LOSS FROM CONTINUING OPERATIONS</t>
         </is>
       </c>
-      <c r="D591" t="inlineStr"/>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E591" t="inlineStr">
         <is>
           <t>-</t>
@@ -55952,7 +55994,11 @@
           <t>Income taxes recovery (expense) 26</t>
         </is>
       </c>
-      <c r="D627" t="inlineStr"/>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E627" s="5" t="n">
         <v>-6.43</v>
       </c>
